--- a/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,47; 35,6</t>
+          <t>21,68; 34,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,97; 87,76</t>
+          <t>75,24; 88,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,08; 77,83</t>
+          <t>61,84; 77,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,52; 41,57</t>
+          <t>27,91; 41,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,55; 35,27</t>
+          <t>21,94; 35,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,97; 92,76</t>
+          <t>82,83; 92,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,75; 81,2</t>
+          <t>66,82; 81,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 53,09</t>
+          <t>28,63; 51,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,18; 32,69</t>
+          <t>23,07; 33,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,22; 89,16</t>
+          <t>80,97; 89,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,28; 77,98</t>
+          <t>67,37; 78,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,64; 44,51</t>
+          <t>30,12; 45,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,14; 37,14</t>
+          <t>24,04; 36,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,72; 87,54</t>
+          <t>76,47; 87,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,97; 75,57</t>
+          <t>63,88; 76,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,95; 46,66</t>
+          <t>32,74; 46,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,56; 35,4</t>
+          <t>23,72; 35,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,4; 85,7</t>
+          <t>75,46; 85,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,53; 82,83</t>
+          <t>73,14; 82,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,49; 51,54</t>
+          <t>39,1; 50,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,5; 33,98</t>
+          <t>25,4; 34,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78,04; 85,62</t>
+          <t>77,47; 85,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,42; 78,27</t>
+          <t>70,46; 78,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,67; 46,49</t>
+          <t>37,84; 46,38</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,02; 36,45</t>
+          <t>22,8; 35,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,66; 89,44</t>
+          <t>77,68; 89,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,72; 61,99</t>
+          <t>48,59; 63,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 25,45</t>
+          <t>12,4; 25,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,41; 37,98</t>
+          <t>23,87; 37,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,02; 91,55</t>
+          <t>81,47; 91,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,43; 60,39</t>
+          <t>45,91; 60,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 25,46</t>
+          <t>15,12; 26,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,44; 35,03</t>
+          <t>25,2; 34,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81,01; 88,88</t>
+          <t>81,71; 88,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,37; 59,96</t>
+          <t>49,5; 59,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 24,36</t>
+          <t>14,55; 23,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,56; 42,71</t>
+          <t>30,54; 43,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,01; 86,79</t>
+          <t>76,13; 86,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,08; 78,94</t>
+          <t>67,04; 78,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,81; 39,11</t>
+          <t>26,46; 39,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,88; 38,9</t>
+          <t>26,99; 38,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,2; 84,73</t>
+          <t>73,74; 84,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,08; 76,47</t>
+          <t>64,01; 75,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 38,23</t>
+          <t>25,53; 37,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 39,14</t>
+          <t>30,45; 39,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,83; 84,35</t>
+          <t>76,84; 84,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,51; 75,71</t>
+          <t>67,02; 76,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,83; 36,37</t>
+          <t>27,44; 36,42</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,18; 35,0</t>
+          <t>28,11; 35,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,61; 85,36</t>
+          <t>79,53; 85,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,57; 71,12</t>
+          <t>64,51; 71,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 34,53</t>
+          <t>26,33; 34,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,54</t>
+          <t>26,77; 33,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,08; 86,23</t>
+          <t>80,5; 85,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,34; 72,76</t>
+          <t>66,23; 72,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,42</t>
+          <t>31,17; 38,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,41; 33,2</t>
+          <t>28,56; 33,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,2; 84,96</t>
+          <t>81,24; 84,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,74; 71,08</t>
+          <t>66,62; 71,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,55</t>
+          <t>30,09; 35,55</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>29231</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79746</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61396</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40503</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33035</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>99042</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76624</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>53057</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>62266</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>178789</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>138020</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>93560</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>22807; 36726</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73084; 85498</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53940; 67835</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32630; 48933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25949; 41481</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>92666; 103765</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>68022; 83429</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>40203; 72070</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>51552; 73787</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>169228; 186688</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>127344; 148298</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>77506; 117087</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>37650</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106485</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105027</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72867</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41248</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>125544</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>135624</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>114494</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>78899</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>232030</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>240650</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>187360</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>30039; 45683</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98637; 112853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>95462; 113699</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>61647; 87055</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33378; 50503</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>116627; 132811</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>126656; 143140</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>99577; 129179</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>67501; 91253</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>219667; 241573</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>227286; 252217</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>167596; 205454</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>31591</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87969</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63329</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37089</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34566</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>101377</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70101</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>37086</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>66156</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>189345</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>133430</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>74175</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>24588; 38543</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>81450; 93610</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55417; 71967</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23612; 48858</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26877; 42376</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>95149; 107053</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>60348; 79070</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>27866; 48684</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>55540; 76699</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>181088; 196902</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>121527; 146548</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>54507; 89454</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>60623</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119606</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>121194</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54225</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51190</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>123837</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>109324</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>56498</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>111813</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>243443</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>230518</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>110724</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>50499; 72227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>111153; 126531</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>110832; 130143</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>44441; 65686</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>42361; 60700</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>114261; 131332</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>99423; 117970</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>45954; 67721</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>98137; 125779</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>231242; 254216</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>214909; 244122</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>95477; 126732</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>159096</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>393806</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>350945</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>204684</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>261135</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>319134</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>843606</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>742618</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>465819</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>141510; 176257</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>379315; 407294</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>332904; 368716</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>174745; 229342</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>141508; 176911</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>433225; 461879</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>372009; 409489</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>236671; 291279</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>294665; 343019</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>824703; 862665</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>717982; 767086</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>428080; 505781</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,68; 34,91</t>
+          <t>21,4; 35,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,24; 88,03</t>
+          <t>74,99; 87,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,84; 77,78</t>
+          <t>61,96; 78,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,91; 41,86</t>
+          <t>27,28; 42,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,94; 35,07</t>
+          <t>21,34; 35,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,83; 92,75</t>
+          <t>82,78; 92,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,82; 81,96</t>
+          <t>66,28; 81,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,63; 51,33</t>
+          <t>28,24; 52,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,07; 33,01</t>
+          <t>23,39; 33,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80,97; 89,32</t>
+          <t>80,72; 89,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,37; 78,46</t>
+          <t>67,82; 78,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,12; 45,5</t>
+          <t>30,59; 44,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,04; 36,56</t>
+          <t>23,99; 35,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,47; 87,49</t>
+          <t>76,35; 87,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,88; 76,09</t>
+          <t>63,71; 75,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,74; 46,23</t>
+          <t>32,57; 46,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,72; 35,88</t>
+          <t>23,5; 35,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,46; 85,93</t>
+          <t>75,68; 85,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,14; 82,66</t>
+          <t>72,96; 82,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,1; 50,73</t>
+          <t>39,0; 51,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,4; 34,34</t>
+          <t>25,44; 34,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77,47; 85,2</t>
+          <t>78,2; 85,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,46; 78,18</t>
+          <t>70,35; 78,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,84; 46,38</t>
+          <t>37,93; 46,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,8; 35,74</t>
+          <t>23,11; 36,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,68; 89,28</t>
+          <t>77,66; 88,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 63,1</t>
+          <t>48,07; 62,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 25,66</t>
+          <t>11,25; 26,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,87; 37,64</t>
+          <t>24,7; 38,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,47; 91,67</t>
+          <t>81,79; 91,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,91; 60,15</t>
+          <t>45,73; 60,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,12; 26,42</t>
+          <t>15,45; 26,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 34,8</t>
+          <t>25,7; 35,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81,71; 88,84</t>
+          <t>81,01; 88,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,5; 59,69</t>
+          <t>49,41; 59,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 23,88</t>
+          <t>15,32; 24,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,54; 43,68</t>
+          <t>29,94; 42,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,13; 86,66</t>
+          <t>76,11; 87,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,04; 78,72</t>
+          <t>67,28; 79,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,46; 39,11</t>
+          <t>26,68; 39,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 38,68</t>
+          <t>26,76; 38,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,74; 84,76</t>
+          <t>74,39; 84,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,01; 75,96</t>
+          <t>64,25; 76,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,53; 37,62</t>
+          <t>25,41; 37,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,45; 39,03</t>
+          <t>30,39; 39,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,84; 84,47</t>
+          <t>77,03; 84,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,02; 76,14</t>
+          <t>67,9; 76,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,42</t>
+          <t>27,63; 36,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,11; 35,02</t>
+          <t>28,48; 34,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,53; 85,39</t>
+          <t>79,67; 85,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,51; 71,45</t>
+          <t>64,84; 71,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,33; 34,56</t>
+          <t>26,65; 34,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,77; 33,47</t>
+          <t>27,52; 34,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,5; 85,83</t>
+          <t>81,05; 86,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,9</t>
+          <t>66,42; 72,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,36</t>
+          <t>30,85; 38,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,24</t>
+          <t>28,59; 33,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,24; 84,98</t>
+          <t>81,03; 84,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,62; 71,17</t>
+          <t>66,66; 71,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,09; 35,55</t>
+          <t>29,96; 35,62</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22807; 36726</t>
+          <t>22515; 37674</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73084; 85498</t>
+          <t>72833; 85248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53940; 67835</t>
+          <t>54040; 68227</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32630; 48933</t>
+          <t>31886; 49230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25949; 41481</t>
+          <t>25238; 41882</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92666; 103765</t>
+          <t>92607; 103834</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68022; 83429</t>
+          <t>67472; 83382</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40203; 72070</t>
+          <t>39652; 73718</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51552; 73787</t>
+          <t>52278; 74027</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169228; 186688</t>
+          <t>168700; 186267</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127344; 148298</t>
+          <t>128183; 147422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77506; 117087</t>
+          <t>78703; 115529</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30039; 45683</t>
+          <t>29976; 44970</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98637; 112853</t>
+          <t>98474; 113157</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95462; 113699</t>
+          <t>95208; 113328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61647; 87055</t>
+          <t>61324; 87340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33378; 50503</t>
+          <t>33067; 50076</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116627; 132811</t>
+          <t>116961; 132189</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126656; 143140</t>
+          <t>126332; 143079</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>99577; 129179</t>
+          <t>99303; 130509</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67501; 91253</t>
+          <t>67586; 90371</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>219667; 241573</t>
+          <t>221725; 242317</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>227286; 252217</t>
+          <t>226948; 252883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>167596; 205454</t>
+          <t>168032; 207118</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24588; 38543</t>
+          <t>24929; 39236</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81450; 93610</t>
+          <t>81427; 93161</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55417; 71967</t>
+          <t>54816; 71486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23612; 48858</t>
+          <t>21412; 49815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26877; 42376</t>
+          <t>27803; 42940</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95149; 107053</t>
+          <t>95512; 107073</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60348; 79070</t>
+          <t>60115; 78904</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27866; 48684</t>
+          <t>28469; 49025</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55540; 76699</t>
+          <t>56655; 77428</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181088; 196902</t>
+          <t>179545; 197218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121527; 146548</t>
+          <t>121300; 144959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54507; 89454</t>
+          <t>57402; 90688</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50499; 72227</t>
+          <t>49505; 70963</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>111153; 126531</t>
+          <t>111121; 127268</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>110832; 130143</t>
+          <t>111227; 130639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44441; 65686</t>
+          <t>44812; 65659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42361; 60700</t>
+          <t>42001; 61083</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114261; 131332</t>
+          <t>115268; 131117</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99423; 117970</t>
+          <t>99791; 118350</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45954; 67721</t>
+          <t>45739; 67674</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98137; 125779</t>
+          <t>97948; 127826</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>231242; 254216</t>
+          <t>231827; 254307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>214909; 244122</t>
+          <t>217730; 244657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95477; 126732</t>
+          <t>96143; 125620</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>141510; 176257</t>
+          <t>143346; 175521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>379315; 407294</t>
+          <t>380002; 407906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>332904; 368716</t>
+          <t>334612; 370677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174745; 229342</t>
+          <t>176846; 228486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>141508; 176911</t>
+          <t>145465; 180130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>433225; 461879</t>
+          <t>436171; 462974</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>372009; 409489</t>
+          <t>373103; 409824</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>236671; 291279</t>
+          <t>234238; 289888</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>294665; 343019</t>
+          <t>295036; 343331</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>824703; 862665</t>
+          <t>822566; 861399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>717982; 767086</t>
+          <t>718387; 767403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>428080; 505781</t>
+          <t>426337; 506888</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39,08%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>27,78%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>82,1%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>70,39%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,4; 35,81</t>
+          <t>21,55; 35,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,99; 87,77</t>
+          <t>82,97; 92,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,96; 78,23</t>
+          <t>65,75; 81,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,28; 42,11</t>
+          <t>30,56; 53,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 35,41</t>
+          <t>21,47; 35,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,78; 92,82</t>
+          <t>74,97; 87,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,28; 81,91</t>
+          <t>61,08; 77,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,24; 52,5</t>
+          <t>27,43; 41,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 33,12</t>
+          <t>23,18; 32,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80,72; 89,12</t>
+          <t>81,22; 89,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,82; 78,0</t>
+          <t>67,28; 77,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,59; 44,9</t>
+          <t>31,4; 44,17</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>30,13%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>82,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>70,28%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>78,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 35,99</t>
+          <t>23,56; 35,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,35; 87,73</t>
+          <t>75,4; 85,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,71; 75,84</t>
+          <t>72,53; 82,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,57; 46,38</t>
+          <t>40,36; 52,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 35,58</t>
+          <t>24,14; 37,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,68; 85,53</t>
+          <t>76,72; 87,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,96; 82,63</t>
+          <t>63,97; 75,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,0; 51,25</t>
+          <t>30,75; 43,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,44; 34,01</t>
+          <t>25,5; 33,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78,2; 85,46</t>
+          <t>78,04; 85,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,35; 78,39</t>
+          <t>70,42; 78,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,93; 46,76</t>
+          <t>37,83; 46,28</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29,29%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>83,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>55,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>53,33%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 36,38</t>
+          <t>24,41; 37,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,66; 88,85</t>
+          <t>81,02; 91,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,07; 62,68</t>
+          <t>46,43; 60,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 26,16</t>
+          <t>15,98; 26,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,7; 38,14</t>
+          <t>23,02; 36,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,79; 91,68</t>
+          <t>77,66; 89,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,73; 60,02</t>
+          <t>47,72; 61,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 26,61</t>
+          <t>17,81; 29,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,7; 35,13</t>
+          <t>25,44; 35,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81,01; 88,98</t>
+          <t>81,01; 88,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,41; 59,05</t>
+          <t>49,37; 59,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 24,21</t>
+          <t>18,66; 26,72</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>36,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>81,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>73,3%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,39%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,94; 42,92</t>
+          <t>26,88; 38,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,11; 87,17</t>
+          <t>74,2; 84,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,28; 79,02</t>
+          <t>64,08; 76,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,68; 39,09</t>
+          <t>26,0; 38,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,76; 38,92</t>
+          <t>30,56; 42,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,39; 84,62</t>
+          <t>76,01; 86,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,25; 76,2</t>
+          <t>67,08; 78,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 37,6</t>
+          <t>27,29; 40,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,39; 39,66</t>
+          <t>30,1; 39,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,03; 84,5</t>
+          <t>76,83; 84,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,9; 76,3</t>
+          <t>67,51; 75,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 36,1</t>
+          <t>28,56; 37,26</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,48; 34,87</t>
+          <t>27,03; 33,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,67; 85,52</t>
+          <t>81,08; 86,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,84; 71,83</t>
+          <t>66,34; 72,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,65; 34,43</t>
+          <t>31,94; 39,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,08</t>
+          <t>28,18; 35,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,05; 86,03</t>
+          <t>79,61; 85,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,42; 72,96</t>
+          <t>64,57; 71,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,85; 38,18</t>
+          <t>29,0; 35,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,59; 33,27</t>
+          <t>28,41; 33,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,03; 84,86</t>
+          <t>81,2; 84,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,66; 71,2</t>
+          <t>66,74; 71,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,96; 35,62</t>
+          <t>31,41; 36,5</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33035</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99042</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76624</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49199</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>29231</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>79746</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>61396</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40503</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33035</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99042</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76624</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53057</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93560</t>
+          <t>90958</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22515; 37674</t>
+          <t>25487; 41723</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72833; 85248</t>
+          <t>92818; 103766</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54040; 68227</t>
+          <t>66927; 82663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31886; 49230</t>
+          <t>38473; 67407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25238; 41882</t>
+          <t>22584; 37453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92607; 103834</t>
+          <t>72814; 85238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67472; 83382</t>
+          <t>53277; 67880</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39652; 73718</t>
+          <t>33118; 50488</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52278; 74027</t>
+          <t>51797; 73070</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>168700; 186267</t>
+          <t>169749; 186333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>128183; 147422</t>
+          <t>127160; 147391</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78703; 115529</t>
+          <t>77445; 108944</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>105</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41248</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125544</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135624</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109281</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>37650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>106485</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>105027</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72867</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41248</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>125544</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>135624</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>67804</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>187360</t>
+          <t>177086</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29976; 44970</t>
+          <t>33165; 49818</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98474; 113157</t>
+          <t>116531; 132447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95208; 113328</t>
+          <t>125595; 143433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61324; 87340</t>
+          <t>95630; 125246</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33067; 50076</t>
+          <t>30163; 46407</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116961; 132189</t>
+          <t>98951; 112910</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126332; 143079</t>
+          <t>95595; 112929</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>99303; 130509</t>
+          <t>56132; 79833</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67586; 90371</t>
+          <t>67768; 90300</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221725; 242317</t>
+          <t>221269; 242763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226948; 252883</t>
+          <t>227166; 252485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>168032; 207118</t>
+          <t>158687; 194123</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34566</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70101</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34767</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>31591</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>87969</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>63329</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37089</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34566</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>101377</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74175</t>
+          <t>71765</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24929; 39236</t>
+          <t>27474; 42757</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81427; 93161</t>
+          <t>94622; 106913</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54816; 71486</t>
+          <t>61040; 79390</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21412; 49815</t>
+          <t>26741; 44282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27803; 42940</t>
+          <t>24825; 39310</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95512; 107073</t>
+          <t>81423; 93778</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60115; 78904</t>
+          <t>54425; 70698</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28469; 49025</t>
+          <t>27969; 46197</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56655; 77428</t>
+          <t>56080; 77222</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179545; 197218</t>
+          <t>179546; 196994</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121300; 144959</t>
+          <t>121200; 147198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57402; 90688</t>
+          <t>60537; 86693</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51190</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123837</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>109324</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54006</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>60623</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>119606</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>121194</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54225</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>51190</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>123837</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>109324</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>109340</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49505; 70963</t>
+          <t>42182; 61055</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>111121; 127268</t>
+          <t>114966; 131289</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111227; 130639</t>
+          <t>99525; 118774</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44812; 65659</t>
+          <t>43741; 65478</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42001; 61083</t>
+          <t>50522; 70612</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115268; 131117</t>
+          <t>110974; 126718</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99791; 118350</t>
+          <t>110903; 130512</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45739; 67674</t>
+          <t>45609; 67295</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97948; 127826</t>
+          <t>97022; 126144</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>231827; 254307</t>
+          <t>231204; 253852</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217730; 244657</t>
+          <t>216463; 242756</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96143; 125620</t>
+          <t>95793; 124962</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>569</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>535</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>305</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>143346; 175521</t>
+          <t>142875; 177263</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>380002; 407906</t>
+          <t>436342; 464031</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>334612; 370677</t>
+          <t>372627; 408700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176846; 228486</t>
+          <t>223101; 272696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>145465; 180130</t>
+          <t>141828; 176193</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>436171; 462974</t>
+          <t>379722; 407139</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>373103; 409824</t>
+          <t>333199; 367020</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>234238; 289888</t>
+          <t>181945; 221074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>295036; 343331</t>
+          <t>293215; 342599</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>822566; 861399</t>
+          <t>824311; 862397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>718387; 767403</t>
+          <t>719347; 766056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>426337; 506888</t>
+          <t>416526; 483894</t>
         </is>
       </c>
     </row>
